--- a/02_加值成品/八上/八上4-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上4-4_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上4-4 光學儀器與視覺　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上4-4 光學儀器與視覺　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>眼睛中相當於凸透鏡的是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視網膜</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>前方</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>水晶體</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>聚光成像</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>影像成在眼睛哪裡？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>望遠鏡</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>視網膜</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>焦距內</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>放大虛像</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>感光</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>視網膜上的像是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>倒立實像</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>處理倒立像</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>顯微鏡</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>經腦處理</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>近視用哪種透鏡矯正？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>倒立實像</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>後方</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>凹透鏡</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>發散</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>遠視用哪種透鏡矯正？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>水晶體</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>凸透鏡成像</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>倒立實像</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>凸透鏡</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>會聚</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>放大鏡成什麼像？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>水晶體</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>放大虛像</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>凸透鏡</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>看微小物體用？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>顯微鏡</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>倒立實像</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>放大虛像</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>放大</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>看遠處物體用？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>望遠鏡</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>顯微鏡</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>後方</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>觀遠</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>人眼看遠看近靠改變什麼？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>凸透鏡成像</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>較厚</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>後移到視網膜</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>水晶體厚薄</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>調節</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>視網膜相當於相機的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>底片/感光元件</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>眼睛長時間調節近距離致眼球變長</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>大腦自動翻轉處理</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>更長,像成更前</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>成像</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上4-4 光學儀器與視覺　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上4-4 光學儀器與視覺　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>近視是像成在視網膜何處？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>前方</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>視網膜</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>眼球太長</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>遠視是像成在視網膜何處？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>視網膜</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>後方</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>倒立實像</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>眼球太短</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>凹透鏡使光線發散讓像？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>前移到視網膜</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>水晶體厚薄</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>水晶體</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>後移到視網膜</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>矯正近視</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>凸透鏡使光線會聚讓像？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>增加近視風險</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>前方</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>前移到視網膜</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>矯正遠視</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>顯微鏡用幾個凸透鏡？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>看遠較清、看近模糊</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>底片/感光元件</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>物鏡成放大實像,目鏡再放大成虛像</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>兩個(物鏡目鏡)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>兩級放大</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>大腦看到正立像是因為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>處理倒立像</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>前方</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>視網膜</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>神經</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>放大鏡要放在物體多近？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>後方</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>顯微鏡</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>焦距內</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>成放大虛像</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>長時間看近物易造成？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>水晶體</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>近視</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>顯微鏡</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>倒立實像</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>用眼過度</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>看近物時水晶體會變？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>水晶體</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>前移到視網膜</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>水晶體厚薄</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>較厚</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>調節</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>矯正遠視需要會聚光的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>凸透鏡</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>顯微鏡</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>焦距內</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>視網膜</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>會聚</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上4-4 光學儀器與視覺　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上4-4 光學儀器與視覺　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何視網膜倒立像我們卻看到正立？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>大腦自動翻轉處理</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>底片/感光元件</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>眼睛長時間調節近距離致眼球變長</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>兩個(物鏡目鏡)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>視覺處理</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>近視度數深表示眼球？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>大腦自動翻轉處理</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>底片/感光元件</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>水晶體調節力下降</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>更長,像成更前</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>需更強凹透鏡</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>顯微鏡物鏡目鏡如何協同？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>更長,像成更前</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>水晶體調節力下降</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>物鏡成放大實像,目鏡再放大成虛像</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>眼睛長時間調節近距離致眼球變長</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>兩級</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>看書距離太近長期會？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>增加近視風險</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>視網膜</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>焦距內</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>凹透鏡</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>護眼</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>遠視者看近模糊看遠清嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>眼睛長時間調節近距離致眼球變長</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>水晶體調節力下降</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>看遠較清、看近模糊</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>兩個(物鏡目鏡)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>特徵</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>放大鏡愈靠近物體像愈？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>前移到視網膜</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>較厚</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>大(焦距內)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>成像</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>折射式望遠鏡用什麼元件？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>焦距內</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>倒立實像</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>望遠鏡</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>凸透鏡</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>物鏡目鏡</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>老花(遠視)為何隨年齡增？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>兩個(物鏡目鏡)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>水晶體調節力下降</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>底片/感光元件</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>物鏡成放大實像,目鏡再放大成虛像</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>老化</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何長時間看手機易近視？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>眼睛長時間調節近距離致眼球變長</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>更長,像成更前</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>物鏡成放大實像,目鏡再放大成虛像</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>看遠較清、看近模糊</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>用眼</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>天文望遠鏡與顯微鏡共同利用？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>凸透鏡成像</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>前移到視網膜</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>焦距內</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>凸透鏡</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>透鏡</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上4-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上4-4_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>聚光成像</t>
+          <t>聚光成像：眼睛內的水晶體形狀像凸透鏡，負責把光線會聚成像，功能上相當於一個凸透鏡</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>感光</t>
+          <t>感光：眼睛內部最後方的視網膜上分布著感光細胞，光線經水晶體會聚後就成像在這裡</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>經腦處理</t>
+          <t>經腦處理：光線經水晶體(凸透鏡)成像時會上下左右交叉，所以視網膜上成的是倒立的實像，之後再由大腦處理成我們感覺到的正立影像</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>發散</t>
+          <t>發散：近視是影像成在視網膜前方，需要用能讓光線先發散的凹透鏡矯正，把焦點往後移到視網膜上</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>會聚</t>
+          <t>會聚：遠視是影像成在視網膜後方，需要用能讓光線提早會聚的凸透鏡矯正，把焦點往前移到視網膜上</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>凸透鏡</t>
+          <t>凸透鏡：放大鏡是凸透鏡，把物體放在焦距以內時，會成一個正立放大的虛像</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>放大</t>
+          <t>放大：顯微鏡利用兩個凸透鏡(物鏡、目鏡)組合，把微小物體逐級放大，才能看清楚肉眼看不到的細節</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>觀遠</t>
+          <t>觀遠：望遠鏡利用凸透鏡組合，把遠處微小的影像放大，讓我們能看清楚遠方的景物</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>調節</t>
+          <t>調節：眼睛裡的水晶體能靠肌肉調節厚薄，看近物時變厚、看遠物時變薄，藉此讓影像清楚對焦在視網膜上</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>成像</t>
+          <t>成像：視網膜是眼睛裡負責感光成像的構造，功能就像相機裡的底片或感光元件，負責接收影像</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>眼球太長</t>
+          <t>眼球太長：近視患者眼球前後距離過長，使影像提早在視網膜前方就聚焦了，之後又發散開來，到達視網膜時已經模糊</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>眼球太短</t>
+          <t>眼球太短：遠視患者眼球前後距離過短，光線還沒會聚完全就已經到達視網膜，理論上的焦點落在視網膜後方</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>矯正近視</t>
+          <t>矯正近視：近視是像成在視網膜前方，先用凹透鏡讓光線發散一些，可以把原本提早聚焦的位置往後推移到剛好落在視網膜上</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>矯正遠視</t>
+          <t>矯正遠視：遠視是像該成在視網膜後方，先用凸透鏡讓光線提早會聚一些，可以把焦點位置往前移到剛好落在視網膜上</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>兩級放大</t>
+          <t>兩級放大：顯微鏡由靠近物體的物鏡和靠近眼睛的目鏡兩個凸透鏡組成，物鏡先把物體放大成一次實像，目鏡再把這個像進一步放大，共兩級放大</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>神經</t>
+          <t>神經：視網膜上實際成的是倒立的像，這個影像訊號經視神經傳到大腦後，會被大腦重新處理翻轉，讓我們感覺看到的是正立的景象</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>成放大虛像</t>
+          <t>成放大虛像：凸透鏡只有在物體放在焦距以內時，才會成正立放大的虛像，這正是放大鏡的使用方式</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>用眼過度</t>
+          <t>用眼過度：長時間近距離用眼，眼睛的水晶體長期維持較厚的調節狀態，可能使眼軸逐漸變長，增加近視的風險</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>調節</t>
+          <t>調節：看近物時，眼睛的睫狀肌收縮，使水晶體變得比較厚，增加折光能力，讓近處影像能清楚成像在視網膜上</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>會聚</t>
+          <t>會聚：遠視是因為影像成在視網膜後方，需要用能讓光線提早會聚的凸透鏡來矯正，把焦點往前移到視網膜上</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>視覺處理</t>
+          <t>視覺處理：眼睛的水晶體(凸透鏡)成像原理使影像在視網膜上呈現倒立，但大腦長期處理這類視覺訊號後，會自動把訊號重新解讀翻轉，讓我們主觀感受到的是正立的世界</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>需更強凹透鏡</t>
+          <t>需更強凹透鏡：近視度數越深，代表眼球前後拉得越長，光線提早聚焦的位置離視網膜越遠，需要用發散能力更強的凹透鏡才能把焦點矯正回視網膜上</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>兩級</t>
+          <t>兩級：靠近物體的物鏡先把物體成一個放大的實像，這個實像剛好落在目鏡的焦距以內，目鏡再把這個實像當成物體，進一步放大成一個更大的虛像供眼睛觀察，兩級透鏡協同運作大幅提高放大倍率</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>護眼</t>
+          <t>護眼：看書距離太近，眼睛的睫狀肌需要長時間收縮讓水晶體維持較厚的狀態，長期下來容易造成眼軸拉長，增加近視的風險</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>特徵</t>
+          <t>特徵：遠視者的水晶體調節能力較弱，看近物需要較大的會聚能力容易對焦不足而模糊，但看遠處物體所需的會聚能力較小，通常還能看得比較清楚</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>成像</t>
+          <t>成像：凸透鏡在焦距以內時，物體離透鏡越近(但仍在焦距內)，成的虛像會越大，這也是使用放大鏡時的常見經驗</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>物鏡目鏡</t>
+          <t>物鏡目鏡：折射式望遠鏡是利用凸透鏡組成的物鏡和目鏡搭配，把遠方微小的影像逐級放大</t>
         </is>
       </c>
     </row>
@@ -1790,17 +1790,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>老花(遠視)為何隨年齡增？</t>
+          <t>老花為何隨年齡增？</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>兩個(物鏡目鏡)</t>
+          <t>水晶體調節力下降</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>水晶體調節力下降</t>
+          <t>物鏡成放大實像,目鏡再放大成虛像</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>物鏡成放大實像,目鏡再放大成虛像</t>
+          <t>眼睛長時間調節近距離致眼球變長</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>老化</t>
+          <t>老化：隨著年齡增長，水晶體的彈性逐漸變差，睫狀肌調節水晶體厚薄的能力也跟著下降，導致看近物時難以對焦清楚，這種現象稱為老花</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>用眼</t>
+          <t>用眼：長時間近距離用眼，睫狀肌持續收縮、水晶體長期維持較厚的狀態，可能使眼軸(眼球前後長度)逐漸變長，導致影像成在視網膜前方，形成近視</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>透鏡</t>
+          <t>透鏡：望遠鏡和顯微鏡都是利用凸透鏡組合(物鏡加目鏡)，分別把遠處或微小的物體放大成像，讓人眼能夠清楚觀察</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上4-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上4-4_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>視網膜</t>
+          <t>倒立實像</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>凹透鏡</t>
+          <t>處理倒立像</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>前方</t>
+          <t>凸透鏡</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>望遠鏡</t>
+          <t>處理倒立像</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>焦距內</t>
+          <t>水晶體</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>放大虛像</t>
+          <t>凸透鏡</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -723,17 +723,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>水晶體</t>
+          <t>望遠鏡</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>凸透鏡成像</t>
+          <t>後方</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>倒立實像</t>
+          <t>視網膜</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -883,17 +883,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>凸透鏡成像</t>
+          <t>前方</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>較厚</t>
+          <t>凹透鏡</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>後移到視網膜</t>
+          <t>凸透鏡</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>前移到視網膜</t>
+          <t>凹透鏡</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>水晶體厚薄</t>
+          <t>凸透鏡</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>水晶體</t>
+          <t>後方</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1159,17 +1159,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>近視</t>
+          <t>較厚</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>增加近視風險</t>
+          <t>凸透鏡成像</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>前方</t>
+          <t>凸透鏡</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>後方</t>
+          <t>視網膜</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>顯微鏡</t>
+          <t>後移到視網膜</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>凸透鏡</t>
+          <t>放大虛像</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>水晶體</t>
+          <t>視網膜</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>顯微鏡</t>
+          <t>大(焦距內)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>倒立實像</t>
+          <t>凹透鏡</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>顯微鏡</t>
+          <t>水晶體</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>焦距內</t>
+          <t>倒立實像</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>視網膜</t>
+          <t>後方</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1640,17 +1640,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>視網膜</t>
+          <t>水晶體</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>焦距內</t>
+          <t>凸透鏡</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>凹透鏡</t>
+          <t>顯微鏡</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>凸透鏡</t>
+          <t>處理倒立像</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>前移到視網膜</t>
+          <t>放大虛像</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>焦距內</t>
+          <t>凹透鏡</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>倒立實像</t>
+          <t>水晶體厚薄</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>望遠鏡</t>
+          <t>後移到視網膜</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1880,17 +1880,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>前移到視網膜</t>
+          <t>前方</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>焦距內</t>
+          <t>增加近視風險</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>凸透鏡</t>
+          <t>顯微鏡</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
